--- a/ftse250_weekly_summary_2026-10-03.xlsx
+++ b/ftse250_weekly_summary_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,25 +424,30 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_change_1w</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>latest_close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>week_ago_close</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>latest_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>latest_close</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>week_ago_close</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>pct_change_1w</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
@@ -456,19 +461,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>VSVS.L</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="D2" t="n">
         <v>451.2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>372.8</v>
       </c>
-      <c r="E2" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1062628</v>
       </c>
     </row>
@@ -480,19 +490,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>IBST.L</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="D3" t="n">
         <v>81.75</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="E3" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1734720</v>
       </c>
     </row>
@@ -504,19 +519,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>JDW.L</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="D4" t="n">
         <v>915</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>810.5</v>
       </c>
-      <c r="E4" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1038488</v>
       </c>
     </row>
@@ -528,19 +548,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MSLH.L</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="D5" t="n">
         <v>170.3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>154</v>
       </c>
-      <c r="E5" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1183232</v>
       </c>
     </row>
@@ -552,19 +577,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>GRG.L</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="D6" t="n">
         <v>2026</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>1861</v>
       </c>
-      <c r="E6" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>990488</v>
       </c>
     </row>
@@ -576,19 +606,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>PSN.L</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="D7" t="n">
         <v>1237.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1154.5</v>
       </c>
-      <c r="E7" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1983481</v>
       </c>
     </row>
@@ -600,19 +635,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>GEN.L</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="D8" t="n">
         <v>283.8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>265.8</v>
       </c>
-      <c r="E8" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>795084</v>
       </c>
     </row>
@@ -624,19 +664,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MAB.L</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="D9" t="n">
         <v>294.5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>277</v>
       </c>
-      <c r="E9" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>310167</v>
       </c>
     </row>
@@ -648,19 +693,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ATG.L</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="D10" t="n">
         <v>457.4</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>434.4</v>
       </c>
-      <c r="E10" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>94085</v>
       </c>
     </row>
@@ -672,19 +722,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>DSCV.L</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D11" t="n">
         <v>850</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>813</v>
       </c>
-      <c r="E11" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>352324</v>
       </c>
     </row>
@@ -696,19 +751,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>TUI1.DE</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="D12" t="n">
         <v>6.9</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>6.6</v>
       </c>
-      <c r="E12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>5117367</v>
       </c>
     </row>
@@ -720,19 +780,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MGAM.L</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="D13" t="n">
         <v>270.5</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>259</v>
       </c>
-      <c r="E13" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>1086493</v>
       </c>
     </row>
@@ -744,19 +809,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ZIG.L</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="D14" t="n">
         <v>447</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>428.5</v>
       </c>
-      <c r="E14" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>397868</v>
       </c>
     </row>
@@ -768,19 +838,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ESNT.L</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="D15" t="n">
         <v>112</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>108.6</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>363555</v>
       </c>
     </row>
@@ -792,19 +867,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CWR.L</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D16" t="n">
         <v>430</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>417.8</v>
       </c>
-      <c r="E16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>2569975</v>
       </c>
     </row>
@@ -816,19 +896,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>FGP.L</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D17" t="n">
         <v>181.4</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>177.5</v>
       </c>
-      <c r="E17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>758297</v>
       </c>
     </row>
@@ -840,19 +925,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>JMAT.L</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D18" t="n">
         <v>2422</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>2372</v>
       </c>
-      <c r="E18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>359140</v>
       </c>
     </row>
@@ -864,19 +954,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>DOM.L</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D19" t="n">
         <v>213.4</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>209.2</v>
       </c>
-      <c r="E19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>557964</v>
       </c>
     </row>
@@ -888,19 +983,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>SSPG.L</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D20" t="n">
         <v>190</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>186.3</v>
       </c>
-      <c r="E20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>1792482</v>
       </c>
     </row>
@@ -912,19 +1012,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MOON.L</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D21" t="n">
         <v>268</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>262.8</v>
       </c>
-      <c r="E21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>1386833</v>
       </c>
     </row>
@@ -936,19 +1041,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BREE.L</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D22" t="n">
         <v>314</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>308.6</v>
       </c>
-      <c r="E22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>588286</v>
       </c>
     </row>
@@ -960,19 +1070,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BWY.L</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="D23" t="n">
         <v>2104</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>2068</v>
       </c>
-      <c r="E23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>423947</v>
       </c>
     </row>
@@ -984,19 +1099,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>TRN.L</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D24" t="n">
         <v>197.3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>194.3</v>
       </c>
-      <c r="E24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>1103001</v>
       </c>
     </row>
@@ -1008,19 +1128,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MEGP.L</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D25" t="n">
         <v>117.8</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>116.2</v>
       </c>
-      <c r="E25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>682625</v>
       </c>
     </row>
@@ -1032,19 +1157,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D26" t="n">
         <v>917</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>905</v>
       </c>
-      <c r="E26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>166997</v>
       </c>
     </row>
@@ -1056,19 +1186,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>GDWN.L</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D27" t="n">
         <v>14220</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>14060</v>
       </c>
-      <c r="E27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>16240</v>
       </c>
     </row>
@@ -1080,19 +1215,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>RHIM.L</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D28" t="n">
         <v>2850</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>2820</v>
       </c>
-      <c r="E28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>44201</v>
       </c>
     </row>
@@ -1104,19 +1244,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>AML.L</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>34.24</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>33.9</v>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>1053391</v>
       </c>
     </row>
@@ -1128,19 +1273,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>EZJ.L</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D30" t="n">
         <v>680.6</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>675</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>4055588</v>
       </c>
     </row>
@@ -1152,19 +1302,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>KLR.L</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D31" t="n">
         <v>3328</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>3306</v>
       </c>
-      <c r="E31" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
         <v>207648</v>
       </c>
     </row>
@@ -1176,19 +1331,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D32" t="n">
         <v>3270</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>3250</v>
       </c>
-      <c r="E32" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>1118942</v>
       </c>
     </row>
@@ -1200,19 +1360,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D33" t="n">
         <v>269.2</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>267.6</v>
       </c>
-      <c r="E33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>4275481</v>
       </c>
     </row>
@@ -1224,19 +1389,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>HAS.L</t>
         </is>
       </c>
       <c r="C34" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D34" t="n">
         <v>64.3</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>63.95</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>2140134</v>
       </c>
     </row>
@@ -1248,19 +1418,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ROR.L</t>
         </is>
       </c>
       <c r="C35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D35" t="n">
         <v>488</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>485.6</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>2453862</v>
       </c>
     </row>
@@ -1272,19 +1447,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CURY.L</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D36" t="n">
         <v>146.8</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>146.1</v>
       </c>
-      <c r="E36" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>1211357</v>
       </c>
     </row>
@@ -1296,19 +1476,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MGNS.L</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D37" t="n">
         <v>4224</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>4208</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>65792</v>
       </c>
     </row>
@@ -1320,19 +1505,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>PETS.L</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D38" t="n">
         <v>212</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>211.2</v>
       </c>
-      <c r="E38" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>726212</v>
       </c>
     </row>
@@ -1344,19 +1534,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>SNR.L</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D39" t="n">
         <v>297</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>296</v>
       </c>
-      <c r="E39" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
         <v>1280743</v>
       </c>
     </row>
@@ -1368,19 +1563,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BBY.L</t>
         </is>
       </c>
       <c r="C40" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D40" t="n">
         <v>937.5</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>935</v>
       </c>
-      <c r="E40" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
         <v>1502461</v>
       </c>
     </row>
@@ -1392,19 +1592,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="C41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D41" t="n">
         <v>559.5</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>559</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
         <v>1968139</v>
       </c>
     </row>
@@ -1416,19 +1621,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>FAN.L</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>639</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
+        <v>639</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>660276</v>
       </c>
     </row>
@@ -1440,19 +1650,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>WOSG.L</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>672.5</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>672.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>404856</v>
       </c>
     </row>
@@ -1464,19 +1679,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MTO.L</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D44" t="n">
         <v>210</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>210.2</v>
       </c>
-      <c r="E44" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F44" t="n">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>1976939</v>
       </c>
     </row>
@@ -1488,19 +1708,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BP.L</t>
         </is>
       </c>
       <c r="C45" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D45" t="n">
         <v>557.8</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>558.5</v>
       </c>
-      <c r="E45" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F45" t="n">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>29515043</v>
       </c>
     </row>
@@ -1512,19 +1737,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>DNLM.L</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="D46" t="n">
         <v>780</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>782</v>
       </c>
-      <c r="E46" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="F46" t="n">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
         <v>370853</v>
       </c>
     </row>
@@ -1536,19 +1766,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>WIZZ.L</t>
         </is>
       </c>
       <c r="C47" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="D47" t="n">
         <v>1052</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>1055</v>
       </c>
-      <c r="E47" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="F47" t="n">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>580239</v>
       </c>
     </row>
@@ -1560,19 +1795,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>HFG.L</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="D48" t="n">
         <v>698.5</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>700.5</v>
       </c>
-      <c r="E48" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="F48" t="n">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
         <v>390707</v>
       </c>
     </row>
@@ -1584,19 +1824,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>SHEL.L</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D49" t="n">
         <v>3596.5</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>3611</v>
       </c>
-      <c r="E49" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="F49" t="n">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>9526836</v>
       </c>
     </row>
@@ -1608,19 +1853,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>MCG.L</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="D50" t="n">
         <v>23.5</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>23.6</v>
       </c>
-      <c r="E50" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="F50" t="n">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>2687127</v>
       </c>
     </row>
@@ -1632,19 +1882,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ELM.L</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="D51" t="n">
         <v>176.6</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>177.4</v>
       </c>
-      <c r="E51" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>1145256</v>
       </c>
     </row>
@@ -1656,19 +1911,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>SMWH.L</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="D52" t="n">
         <v>369</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>371</v>
       </c>
-      <c r="E52" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="F52" t="n">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
         <v>561586</v>
       </c>
     </row>
@@ -1680,19 +1940,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CWK.L</t>
         </is>
       </c>
       <c r="C53" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D53" t="n">
         <v>5000</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>5030</v>
       </c>
-      <c r="E53" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F53" t="n">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
         <v>180028</v>
       </c>
     </row>
@@ -1704,19 +1969,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>STEM.L</t>
         </is>
       </c>
       <c r="C54" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="D54" t="n">
         <v>300</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>302</v>
       </c>
-      <c r="E54" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="F54" t="n">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>167317</v>
       </c>
     </row>
@@ -1728,19 +1998,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>COA.L</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="D55" t="n">
         <v>80.45</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>81.15000000000001</v>
       </c>
-      <c r="E55" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
         <v>2728688</v>
       </c>
     </row>
@@ -1752,19 +2027,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>EVOK.L</t>
         </is>
       </c>
       <c r="C56" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="D56" t="n">
         <v>42.6</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>43</v>
       </c>
-      <c r="E56" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="F56" t="n">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>5330635</v>
       </c>
     </row>
@@ -1776,19 +2056,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>SRP.L</t>
         </is>
       </c>
       <c r="C57" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D57" t="n">
         <v>251.8</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>254.2</v>
       </c>
-      <c r="E57" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="F57" t="n">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>840281</v>
       </c>
     </row>
@@ -1800,19 +2085,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CHG.L</t>
         </is>
       </c>
       <c r="C58" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="D58" t="n">
         <v>529</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>535.5</v>
       </c>
-      <c r="E58" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="F58" t="n">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>2124655</v>
       </c>
     </row>
@@ -1824,19 +2114,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>GNC.L</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="D59" t="n">
         <v>244.4</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>247.8</v>
       </c>
-      <c r="E59" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="F59" t="n">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>2308814</v>
       </c>
     </row>
@@ -1848,19 +2143,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CRST.L</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="D60" t="n">
         <v>58</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>59</v>
       </c>
-      <c r="E60" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="F60" t="n">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
         <v>2488392</v>
       </c>
     </row>
@@ -1872,19 +2172,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>DOCS.L</t>
         </is>
       </c>
       <c r="C61" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="D61" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>67.8</v>
       </c>
-      <c r="E61" t="n">
-        <v>-1.77</v>
-      </c>
-      <c r="F61" t="n">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>562887</v>
       </c>
     </row>
@@ -1896,19 +2201,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>HTG.L</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="D62" t="n">
         <v>383</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>390</v>
       </c>
-      <c r="E62" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="F62" t="n">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
         <v>221846</v>
       </c>
     </row>
@@ -1920,19 +2230,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ASC.L</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="D63" t="n">
         <v>498</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>508</v>
       </c>
-      <c r="E63" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="F63" t="n">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
         <v>578859</v>
       </c>
     </row>
@@ -1944,19 +2259,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>GAW.L</t>
         </is>
       </c>
       <c r="C64" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="D64" t="n">
         <v>17190</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>17570</v>
       </c>
-      <c r="E64" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="F64" t="n">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>54777</v>
       </c>
     </row>
@@ -1968,19 +2288,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>TPK.L</t>
         </is>
       </c>
       <c r="C65" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="D65" t="n">
         <v>585</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>598.5</v>
       </c>
-      <c r="E65" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="F65" t="n">
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
         <v>506442</v>
       </c>
     </row>
@@ -1992,19 +2317,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>PZC.L</t>
         </is>
       </c>
       <c r="C66" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="D66" t="n">
         <v>95</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>97.2</v>
       </c>
-      <c r="E66" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="F66" t="n">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>920354</v>
       </c>
     </row>
@@ -2016,19 +2346,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CKN.L</t>
         </is>
       </c>
       <c r="C67" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="D67" t="n">
         <v>5030</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
         <v>5150</v>
       </c>
-      <c r="E67" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="F67" t="n">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
         <v>58427</v>
       </c>
     </row>
@@ -2040,19 +2375,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>QQ.L</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="D68" t="n">
         <v>476</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
         <v>489.2</v>
       </c>
-      <c r="E68" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="F68" t="n">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
         <v>1360574</v>
       </c>
     </row>
@@ -2064,19 +2404,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>PAGE.L</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="D69" t="n">
         <v>212.6</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
         <v>219.2</v>
       </c>
-      <c r="E69" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="F69" t="n">
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
         <v>531330</v>
       </c>
     </row>
@@ -2088,19 +2433,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ENOG.L</t>
         </is>
       </c>
       <c r="C70" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="D70" t="n">
         <v>696</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
         <v>718</v>
       </c>
-      <c r="E70" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="F70" t="n">
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
         <v>214972</v>
       </c>
     </row>
@@ -2112,19 +2462,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>GFTU.L</t>
         </is>
       </c>
       <c r="C71" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="D71" t="n">
         <v>934.3</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
         <v>963.9</v>
       </c>
-      <c r="E71" t="n">
-        <v>-3.07</v>
-      </c>
-      <c r="F71" t="n">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
         <v>552435</v>
       </c>
     </row>
@@ -2136,19 +2491,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>DEC.L</t>
         </is>
       </c>
       <c r="C72" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="D72" t="n">
         <v>1012</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
         <v>1046</v>
       </c>
-      <c r="E72" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="F72" t="n">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
         <v>51770</v>
       </c>
     </row>
@@ -2160,19 +2520,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="C73" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="D73" t="n">
         <v>275.4</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
         <v>285.4</v>
       </c>
-      <c r="E73" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F73" t="n">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
         <v>1453229</v>
       </c>
     </row>
@@ -2184,19 +2549,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>PTEC.L</t>
         </is>
       </c>
       <c r="C74" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="D74" t="n">
         <v>374.2</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>388.6</v>
       </c>
-      <c r="E74" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="F74" t="n">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
         <v>390894</v>
       </c>
     </row>
@@ -2208,19 +2578,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BOY.L</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="D75" t="n">
         <v>910.5</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>946.5</v>
       </c>
-      <c r="E75" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="F75" t="n">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
         <v>881812</v>
       </c>
     </row>
@@ -2232,19 +2607,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>PFD.L</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="D76" t="n">
         <v>187.5</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>195.1</v>
       </c>
-      <c r="E76" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="F76" t="n">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
         <v>1577778</v>
       </c>
     </row>
@@ -2256,19 +2636,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>INCH.L</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="D77" t="n">
         <v>739.5</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>770</v>
       </c>
-      <c r="E77" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="F77" t="n">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
         <v>586048</v>
       </c>
     </row>
@@ -2280,19 +2665,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>FXPO.L</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D78" t="n">
         <v>31.18</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>32.48</v>
       </c>
-      <c r="E78" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F78" t="n">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
         <v>3654283</v>
       </c>
     </row>
@@ -2304,19 +2694,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BAB.L</t>
         </is>
       </c>
       <c r="C79" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="D79" t="n">
         <v>922.2</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>988.2</v>
       </c>
-      <c r="E79" t="n">
-        <v>-6.68</v>
-      </c>
-      <c r="F79" t="n">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
         <v>1178445</v>
       </c>
     </row>
@@ -2328,19 +2723,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>VTY.L</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="D80" t="n">
         <v>241.6</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>259</v>
       </c>
-      <c r="E80" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="F80" t="n">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
         <v>1559121</v>
       </c>
     </row>
@@ -2352,19 +2752,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>CCR.L</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="D81" t="n">
         <v>97</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>104</v>
       </c>
-      <c r="E81" t="n">
-        <v>-6.73</v>
-      </c>
-      <c r="F81" t="n">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
         <v>797883</v>
       </c>
     </row>
@@ -2376,19 +2781,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:00</t>
+          <t>BAG.L</t>
         </is>
       </c>
       <c r="C82" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="D82" t="n">
         <v>542</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
         <v>594</v>
       </c>
-      <c r="E82" t="n">
-        <v>-8.75</v>
-      </c>
-      <c r="F82" t="n">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
         <v>569387</v>
       </c>
     </row>

--- a/ftse250_weekly_summary_2026-10-03.xlsx
+++ b/ftse250_weekly_summary_2026-10-03.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VSVS.L</t>
+          <t>Vesuvius plc</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBST.L</t>
+          <t>Ibstock plc</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -519,7 +519,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JDW.L</t>
+          <t>J D Wetherspoon plc</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -548,7 +548,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSLH.L</t>
+          <t>Marshalls plc</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GRG.L</t>
+          <t>Greggs plc</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PSN.L</t>
+          <t>Persimmon Plc</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEN.L</t>
+          <t>Genuit Group plc</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAB.L</t>
+          <t>Mitchells &amp; Butlers plc</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -693,7 +693,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATG.L</t>
+          <t>Auction Technology Group plc</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DSCV.L</t>
+          <t>discoverIE Group plc</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TUI1.DE</t>
+          <t>TUI AG</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MGAM.L</t>
+          <t>Morgan Advanced Materials plc</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZIG.L</t>
+          <t>Zigup Plc</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -838,7 +838,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESNT.L</t>
+          <t>Essentra plc</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -867,7 +867,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CWR.L</t>
+          <t>Ceres Power Holdings plc</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FGP.L</t>
+          <t>FirstGroup plc</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JMAT.L</t>
+          <t>Johnson Matthey Plc</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DOM.L</t>
+          <t>Domino's Pizza Group plc</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSPG.L</t>
+          <t>SSP Group plc</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MOON.L</t>
+          <t>Moonpig Group plc</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BREE.L</t>
+          <t>Breedon Group plc</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BWY.L</t>
+          <t>Bellway p.l.c.</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRN.L</t>
+          <t>Trainline Plc</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MEGP.L</t>
+          <t>ME Group International plc</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>Victrex plc</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GDWN.L</t>
+          <t>Goodwin PLC</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RHIM.L</t>
+          <t>RHI Magnesita N.V.</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AML.L</t>
+          <t>Aston Martin Lagonda global Holdings plc</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EZJ.L</t>
+          <t>easyJet plc</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KLR.L</t>
+          <t>Keller Group plc</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>Hill &amp; Smith PLC</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HAS.L</t>
+          <t>Hays plc</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ROR.L</t>
+          <t>Rotork plc</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CURY.L</t>
+          <t>Currys plc</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MGNS.L</t>
+          <t>Morgan Sindall Group plc</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PETS.L</t>
+          <t>Pets at Home Group Plc</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SNR.L</t>
+          <t>Senior plc</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BBY.L</t>
+          <t>Balfour Beatty plc</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>Tate &amp; Lyle plc</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FAN.L</t>
+          <t>Volution Group plc</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WOSG.L</t>
+          <t>Watches of Switzerland Group plc</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MTO.L</t>
+          <t>Mitie Group plc</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BP.L</t>
+          <t>BP p.l.c.</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DNLM.L</t>
+          <t>Dunelm Group plc</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WIZZ.L</t>
+          <t>Wizz Air Holdings Plc</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HFG.L</t>
+          <t>Hilton Food Group plc</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SHEL.L</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MCG.L</t>
+          <t>Mobico Group Plc</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ELM.L</t>
+          <t>Elementis plc</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SMWH.L</t>
+          <t>WH Smith PLC</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CWK.L</t>
+          <t>Cranswick plc</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>STEM.L</t>
+          <t>SThree plc</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COA.L</t>
+          <t>Coats Group plc</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EVOK.L</t>
+          <t>evoke plc</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SRP.L</t>
+          <t>Serco Group plc</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CHG.L</t>
+          <t>Chemring Group PLC</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GNC.L</t>
+          <t>Greencore Group plc</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CRST.L</t>
+          <t>Crest Nicholson Holdings plc</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DOCS.L</t>
+          <t>Dr. Martens plc</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HTG.L</t>
+          <t>Hunting PLC</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ASC.L</t>
+          <t>Ardmore Shipping Corporation</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GAW.L</t>
+          <t>Games Workshop Group PLC</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TPK.L</t>
+          <t>Travis Perkins plc</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PZC.L</t>
+          <t>PZ Cussons Plc</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CKN.L</t>
+          <t>Clarkson PLC</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>QQ.L</t>
+          <t>QinetiQ Group plc</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PAGE.L</t>
+          <t>PageGroup plc</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ENOG.L</t>
+          <t>Energean plc</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GFTU.L</t>
+          <t>Grafton Group plc</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DEC.L</t>
+          <t>Diversified Energy Company PLC</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>Ithaca Energy plc</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PTEC.L</t>
+          <t>Playtech plc</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BOY.L</t>
+          <t>Bodycote plc</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PFD.L</t>
+          <t>Premier Foods plc</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>INCH.L</t>
+          <t>Inchcape plc</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FXPO.L</t>
+          <t>Ferrexpo plc</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BAB.L</t>
+          <t>Babcock International Group PLC</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VTY.L</t>
+          <t>Vistry Group PLC</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CCR.L</t>
+          <t>C&amp;C Group plc</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BAG.L</t>
+          <t>A.G. BARR p.l.c.</t>
         </is>
       </c>
       <c r="C82" t="n">
